--- a/Calendário 3DS - BOSCH.xlsx
+++ b/Calendário 3DS - BOSCH.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\27120642839\Documents\projetos_documentacao\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\desktop\Desktop\SENAI\02 - Disciplinas\fim_semestre_2026_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91351109-9EA3-4944-B3D0-40AA47CEB48E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{381F5E3A-9A91-4EE4-8C2B-A236E447FDC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{0F0A21FB-E8CD-4435-8A76-5A26D62A4075}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{0F0A21FB-E8CD-4435-8A76-5A26D62A4075}"/>
   </bookViews>
   <sheets>
     <sheet name="Geral" sheetId="1" r:id="rId1"/>
@@ -31,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="41">
   <si>
     <t>D</t>
   </si>
@@ -317,6 +320,12 @@
   <si>
     <t>Formatura</t>
   </si>
+  <si>
+    <t>Professor estará em São Paulo</t>
+  </si>
+  <si>
+    <t>Data máxima entrega TCC</t>
+  </si>
 </sst>
 </file>
 
@@ -441,7 +450,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -517,6 +526,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -654,7 +669,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -714,123 +729,123 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -903,16 +918,19 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -939,9 +957,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -979,7 +997,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1085,7 +1103,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1227,7 +1245,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2344,31 +2362,31 @@
       <c r="F21"/>
     </row>
     <row r="23" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22" t="s">
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22" t="s">
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="I23" s="22"/>
-      <c r="J23" s="22"/>
-      <c r="K23" s="22" t="s">
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="L23" s="22"/>
-      <c r="M23" s="22"/>
-      <c r="N23" s="22" t="s">
+      <c r="L23" s="30"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="O23" s="22"/>
-      <c r="P23" s="22"/>
+      <c r="O23" s="30"/>
+      <c r="P23" s="30"/>
       <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
       <c r="S23" s="2"/>
@@ -2399,121 +2417,121 @@
       <c r="AR23" s="2"/>
     </row>
     <row r="24" spans="2:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="23" t="s">
+      <c r="B24" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="24"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="32" t="s">
+      <c r="C24" s="33"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="F24" s="33"/>
-      <c r="G24" s="34"/>
-      <c r="H24" s="41"/>
-      <c r="I24" s="42"/>
-      <c r="J24" s="43"/>
-      <c r="K24" s="50" t="s">
+      <c r="F24" s="42"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="50"/>
+      <c r="I24" s="51"/>
+      <c r="J24" s="52"/>
+      <c r="K24" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="L24" s="51"/>
-      <c r="M24" s="52"/>
-      <c r="N24" s="50" t="s">
+      <c r="L24" s="22"/>
+      <c r="M24" s="23"/>
+      <c r="N24" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="O24" s="51"/>
-      <c r="P24" s="52"/>
+      <c r="O24" s="22"/>
+      <c r="P24" s="23"/>
     </row>
     <row r="25" spans="2:44" x14ac:dyDescent="0.25">
-      <c r="B25" s="26"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="36"/>
-      <c r="G25" s="37"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="45"/>
-      <c r="J25" s="46"/>
-      <c r="K25" s="53"/>
-      <c r="L25" s="54"/>
-      <c r="M25" s="55"/>
-      <c r="N25" s="53"/>
-      <c r="O25" s="54"/>
-      <c r="P25" s="55"/>
+      <c r="B25" s="35"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="53"/>
+      <c r="I25" s="54"/>
+      <c r="J25" s="55"/>
+      <c r="K25" s="24"/>
+      <c r="L25" s="25"/>
+      <c r="M25" s="26"/>
+      <c r="N25" s="24"/>
+      <c r="O25" s="25"/>
+      <c r="P25" s="26"/>
     </row>
     <row r="26" spans="2:44" x14ac:dyDescent="0.25">
-      <c r="B26" s="26"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="36"/>
-      <c r="G26" s="37"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="45"/>
-      <c r="J26" s="46"/>
-      <c r="K26" s="53"/>
-      <c r="L26" s="54"/>
-      <c r="M26" s="55"/>
-      <c r="N26" s="53"/>
-      <c r="O26" s="54"/>
-      <c r="P26" s="55"/>
+      <c r="B26" s="35"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="44"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="46"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="54"/>
+      <c r="J26" s="55"/>
+      <c r="K26" s="24"/>
+      <c r="L26" s="25"/>
+      <c r="M26" s="26"/>
+      <c r="N26" s="24"/>
+      <c r="O26" s="25"/>
+      <c r="P26" s="26"/>
     </row>
     <row r="27" spans="2:44" x14ac:dyDescent="0.25">
-      <c r="B27" s="26"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="35"/>
-      <c r="F27" s="36"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="47"/>
-      <c r="I27" s="48"/>
-      <c r="J27" s="49"/>
-      <c r="K27" s="53"/>
-      <c r="L27" s="54"/>
-      <c r="M27" s="55"/>
-      <c r="N27" s="53"/>
-      <c r="O27" s="54"/>
-      <c r="P27" s="55"/>
+      <c r="B27" s="35"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="44"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="56"/>
+      <c r="I27" s="57"/>
+      <c r="J27" s="58"/>
+      <c r="K27" s="24"/>
+      <c r="L27" s="25"/>
+      <c r="M27" s="26"/>
+      <c r="N27" s="24"/>
+      <c r="O27" s="25"/>
+      <c r="P27" s="26"/>
     </row>
     <row r="28" spans="2:44" x14ac:dyDescent="0.25">
-      <c r="B28" s="29"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="40"/>
-      <c r="H28" s="59" t="s">
+      <c r="B28" s="38"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="48"/>
+      <c r="G28" s="49"/>
+      <c r="H28" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="I28" s="59"/>
-      <c r="J28" s="59"/>
-      <c r="K28" s="56"/>
-      <c r="L28" s="57"/>
-      <c r="M28" s="58"/>
-      <c r="N28" s="56"/>
-      <c r="O28" s="57"/>
-      <c r="P28" s="58"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="27"/>
+      <c r="L28" s="28"/>
+      <c r="M28" s="29"/>
+      <c r="N28" s="27"/>
+      <c r="O28" s="28"/>
+      <c r="P28" s="29"/>
     </row>
     <row r="29" spans="2:44" x14ac:dyDescent="0.25">
-      <c r="B29" s="21"/>
-      <c r="C29" s="21"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="21"/>
-      <c r="I29" s="21"/>
-      <c r="J29" s="21"/>
-      <c r="K29" s="21"/>
-      <c r="L29" s="21"/>
-      <c r="M29" s="21"/>
-      <c r="N29" s="21"/>
-      <c r="O29" s="21"/>
-      <c r="P29" s="21"/>
+      <c r="B29" s="59"/>
+      <c r="C29" s="59"/>
+      <c r="D29" s="59"/>
+      <c r="E29" s="59"/>
+      <c r="F29" s="59"/>
+      <c r="G29" s="59"/>
+      <c r="H29" s="59"/>
+      <c r="I29" s="59"/>
+      <c r="J29" s="59"/>
+      <c r="K29" s="59"/>
+      <c r="L29" s="59"/>
+      <c r="M29" s="59"/>
+      <c r="N29" s="59"/>
+      <c r="O29" s="59"/>
+      <c r="P29" s="59"/>
     </row>
     <row r="30" spans="2:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="41"/>
-      <c r="C30" s="42"/>
-      <c r="D30" s="43"/>
+      <c r="B30" s="50"/>
+      <c r="C30" s="51"/>
+      <c r="D30" s="52"/>
       <c r="E30" s="60" t="s">
         <v>17</v>
       </c>
@@ -2524,34 +2542,34 @@
       </c>
       <c r="I30" s="70"/>
       <c r="J30" s="71"/>
-      <c r="K30" s="41"/>
-      <c r="L30" s="42"/>
-      <c r="M30" s="43"/>
-      <c r="N30" s="41"/>
-      <c r="O30" s="42"/>
-      <c r="P30" s="43"/>
+      <c r="K30" s="50"/>
+      <c r="L30" s="51"/>
+      <c r="M30" s="52"/>
+      <c r="N30" s="50"/>
+      <c r="O30" s="51"/>
+      <c r="P30" s="52"/>
     </row>
     <row r="31" spans="2:44" x14ac:dyDescent="0.25">
-      <c r="B31" s="44"/>
-      <c r="C31" s="45"/>
-      <c r="D31" s="46"/>
+      <c r="B31" s="53"/>
+      <c r="C31" s="54"/>
+      <c r="D31" s="55"/>
       <c r="E31" s="63"/>
       <c r="F31" s="64"/>
       <c r="G31" s="65"/>
       <c r="H31" s="72"/>
       <c r="I31" s="73"/>
       <c r="J31" s="74"/>
-      <c r="K31" s="44"/>
-      <c r="L31" s="45"/>
-      <c r="M31" s="46"/>
-      <c r="N31" s="44"/>
-      <c r="O31" s="45"/>
-      <c r="P31" s="46"/>
+      <c r="K31" s="53"/>
+      <c r="L31" s="54"/>
+      <c r="M31" s="55"/>
+      <c r="N31" s="53"/>
+      <c r="O31" s="54"/>
+      <c r="P31" s="55"/>
     </row>
     <row r="32" spans="2:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="44"/>
-      <c r="C32" s="45"/>
-      <c r="D32" s="46"/>
+      <c r="B32" s="53"/>
+      <c r="C32" s="54"/>
+      <c r="D32" s="55"/>
       <c r="E32" s="63"/>
       <c r="F32" s="64"/>
       <c r="G32" s="65"/>
@@ -2560,46 +2578,46 @@
       </c>
       <c r="I32" s="76"/>
       <c r="J32" s="77"/>
-      <c r="K32" s="44"/>
-      <c r="L32" s="45"/>
-      <c r="M32" s="46"/>
-      <c r="N32" s="44"/>
-      <c r="O32" s="45"/>
-      <c r="P32" s="46"/>
+      <c r="K32" s="53"/>
+      <c r="L32" s="54"/>
+      <c r="M32" s="55"/>
+      <c r="N32" s="53"/>
+      <c r="O32" s="54"/>
+      <c r="P32" s="55"/>
     </row>
     <row r="33" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B33" s="44"/>
-      <c r="C33" s="45"/>
-      <c r="D33" s="46"/>
+      <c r="B33" s="53"/>
+      <c r="C33" s="54"/>
+      <c r="D33" s="55"/>
       <c r="E33" s="63"/>
       <c r="F33" s="64"/>
       <c r="G33" s="65"/>
       <c r="H33" s="78"/>
       <c r="I33" s="79"/>
       <c r="J33" s="80"/>
-      <c r="K33" s="44"/>
-      <c r="L33" s="45"/>
-      <c r="M33" s="46"/>
-      <c r="N33" s="44"/>
-      <c r="O33" s="45"/>
-      <c r="P33" s="46"/>
+      <c r="K33" s="53"/>
+      <c r="L33" s="54"/>
+      <c r="M33" s="55"/>
+      <c r="N33" s="53"/>
+      <c r="O33" s="54"/>
+      <c r="P33" s="55"/>
     </row>
     <row r="34" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B34" s="47"/>
-      <c r="C34" s="48"/>
-      <c r="D34" s="49"/>
+      <c r="B34" s="56"/>
+      <c r="C34" s="57"/>
+      <c r="D34" s="58"/>
       <c r="E34" s="66"/>
       <c r="F34" s="67"/>
       <c r="G34" s="68"/>
       <c r="H34" s="81"/>
       <c r="I34" s="82"/>
       <c r="J34" s="83"/>
-      <c r="K34" s="47"/>
-      <c r="L34" s="48"/>
-      <c r="M34" s="49"/>
-      <c r="N34" s="47"/>
-      <c r="O34" s="48"/>
-      <c r="P34" s="49"/>
+      <c r="K34" s="56"/>
+      <c r="L34" s="57"/>
+      <c r="M34" s="58"/>
+      <c r="N34" s="56"/>
+      <c r="O34" s="57"/>
+      <c r="P34" s="58"/>
     </row>
     <row r="37" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
@@ -2607,20 +2625,20 @@
       </c>
     </row>
     <row r="39" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B39" s="85" t="s">
+      <c r="B39" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="85"/>
-      <c r="D39" s="85" t="s">
+      <c r="C39" s="84"/>
+      <c r="D39" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="E39" s="85"/>
-      <c r="F39" s="85" t="s">
+      <c r="E39" s="84"/>
+      <c r="F39" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="G39" s="85"/>
-      <c r="H39" s="85"/>
-      <c r="I39" s="85"/>
+      <c r="G39" s="84"/>
+      <c r="H39" s="84"/>
+      <c r="I39" s="84"/>
       <c r="J39" s="86" t="s">
         <v>22</v>
       </c>
@@ -2629,75 +2647,47 @@
         <v>23</v>
       </c>
       <c r="M39" s="86"/>
-      <c r="N39" s="85" t="s">
+      <c r="N39" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="O39" s="85"/>
-      <c r="P39" s="85"/>
-      <c r="Q39" s="85"/>
+      <c r="O39" s="84"/>
+      <c r="P39" s="84"/>
+      <c r="Q39" s="84"/>
     </row>
     <row r="40" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B40" s="85">
+      <c r="B40" s="84">
         <v>120</v>
       </c>
-      <c r="C40" s="85"/>
-      <c r="D40" s="85">
+      <c r="C40" s="84"/>
+      <c r="D40" s="84">
         <v>20</v>
       </c>
-      <c r="E40" s="85"/>
-      <c r="F40" s="85">
+      <c r="E40" s="84"/>
+      <c r="F40" s="84">
         <v>8</v>
       </c>
-      <c r="G40" s="85"/>
-      <c r="H40" s="85"/>
-      <c r="I40" s="85"/>
+      <c r="G40" s="84"/>
+      <c r="H40" s="84"/>
+      <c r="I40" s="84"/>
       <c r="J40" s="87">
         <v>3.125E-2</v>
       </c>
-      <c r="K40" s="85"/>
+      <c r="K40" s="84"/>
       <c r="L40" s="87">
         <f>J40*F40</f>
         <v>0.25</v>
       </c>
-      <c r="M40" s="85"/>
-      <c r="N40" s="84">
+      <c r="M40" s="84"/>
+      <c r="N40" s="85">
         <f>L40*D40</f>
         <v>5</v>
       </c>
-      <c r="O40" s="84"/>
-      <c r="P40" s="84"/>
-      <c r="Q40" s="84"/>
+      <c r="O40" s="85"/>
+      <c r="P40" s="85"/>
+      <c r="Q40" s="85"/>
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="B12:H12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="R12:X12"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="J2:P2"/>
-    <mergeCell ref="R2:X2"/>
-    <mergeCell ref="N24:P28"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:G23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="K23:M23"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="B24:D28"/>
-    <mergeCell ref="E24:G28"/>
-    <mergeCell ref="H24:J27"/>
-    <mergeCell ref="K24:M28"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="K29:M29"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="B30:D34"/>
-    <mergeCell ref="E30:G34"/>
-    <mergeCell ref="K30:M34"/>
-    <mergeCell ref="N30:P34"/>
-    <mergeCell ref="H30:J31"/>
-    <mergeCell ref="H32:J34"/>
     <mergeCell ref="N39:Q39"/>
     <mergeCell ref="N40:Q40"/>
     <mergeCell ref="B39:C39"/>
@@ -2710,6 +2700,34 @@
     <mergeCell ref="L40:M40"/>
     <mergeCell ref="F39:I39"/>
     <mergeCell ref="F40:I40"/>
+    <mergeCell ref="B30:D34"/>
+    <mergeCell ref="E30:G34"/>
+    <mergeCell ref="K30:M34"/>
+    <mergeCell ref="N30:P34"/>
+    <mergeCell ref="H30:J31"/>
+    <mergeCell ref="H32:J34"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="K29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="N24:P28"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="K23:M23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="B24:D28"/>
+    <mergeCell ref="E24:G28"/>
+    <mergeCell ref="H24:J27"/>
+    <mergeCell ref="K24:M28"/>
+    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="R12:X12"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="J2:P2"/>
+    <mergeCell ref="R2:X2"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -3833,31 +3851,31 @@
       <c r="F21"/>
     </row>
     <row r="23" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22" t="s">
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22" t="s">
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="I23" s="22"/>
-      <c r="J23" s="22"/>
-      <c r="K23" s="22" t="s">
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="L23" s="22"/>
-      <c r="M23" s="22"/>
-      <c r="N23" s="22" t="s">
+      <c r="L23" s="30"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="O23" s="22"/>
-      <c r="P23" s="22"/>
+      <c r="O23" s="30"/>
+      <c r="P23" s="30"/>
       <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
       <c r="S23" s="2"/>
@@ -3888,121 +3906,121 @@
       <c r="AR23" s="2"/>
     </row>
     <row r="24" spans="2:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="23" t="s">
+      <c r="B24" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="24"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="32" t="s">
+      <c r="C24" s="33"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="F24" s="33"/>
-      <c r="G24" s="34"/>
-      <c r="H24" s="41"/>
-      <c r="I24" s="42"/>
-      <c r="J24" s="43"/>
-      <c r="K24" s="50" t="s">
+      <c r="F24" s="42"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="50"/>
+      <c r="I24" s="51"/>
+      <c r="J24" s="52"/>
+      <c r="K24" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="L24" s="51"/>
-      <c r="M24" s="52"/>
-      <c r="N24" s="50" t="s">
+      <c r="L24" s="22"/>
+      <c r="M24" s="23"/>
+      <c r="N24" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="O24" s="51"/>
-      <c r="P24" s="52"/>
+      <c r="O24" s="22"/>
+      <c r="P24" s="23"/>
     </row>
     <row r="25" spans="2:44" x14ac:dyDescent="0.25">
-      <c r="B25" s="26"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="36"/>
-      <c r="G25" s="37"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="45"/>
-      <c r="J25" s="46"/>
-      <c r="K25" s="53"/>
-      <c r="L25" s="54"/>
-      <c r="M25" s="55"/>
-      <c r="N25" s="53"/>
-      <c r="O25" s="54"/>
-      <c r="P25" s="55"/>
+      <c r="B25" s="35"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="53"/>
+      <c r="I25" s="54"/>
+      <c r="J25" s="55"/>
+      <c r="K25" s="24"/>
+      <c r="L25" s="25"/>
+      <c r="M25" s="26"/>
+      <c r="N25" s="24"/>
+      <c r="O25" s="25"/>
+      <c r="P25" s="26"/>
     </row>
     <row r="26" spans="2:44" x14ac:dyDescent="0.25">
-      <c r="B26" s="26"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="36"/>
-      <c r="G26" s="37"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="45"/>
-      <c r="J26" s="46"/>
-      <c r="K26" s="53"/>
-      <c r="L26" s="54"/>
-      <c r="M26" s="55"/>
-      <c r="N26" s="53"/>
-      <c r="O26" s="54"/>
-      <c r="P26" s="55"/>
+      <c r="B26" s="35"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="44"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="46"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="54"/>
+      <c r="J26" s="55"/>
+      <c r="K26" s="24"/>
+      <c r="L26" s="25"/>
+      <c r="M26" s="26"/>
+      <c r="N26" s="24"/>
+      <c r="O26" s="25"/>
+      <c r="P26" s="26"/>
     </row>
     <row r="27" spans="2:44" x14ac:dyDescent="0.25">
-      <c r="B27" s="26"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="35"/>
-      <c r="F27" s="36"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="47"/>
-      <c r="I27" s="48"/>
-      <c r="J27" s="49"/>
-      <c r="K27" s="53"/>
-      <c r="L27" s="54"/>
-      <c r="M27" s="55"/>
-      <c r="N27" s="53"/>
-      <c r="O27" s="54"/>
-      <c r="P27" s="55"/>
+      <c r="B27" s="35"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="44"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="56"/>
+      <c r="I27" s="57"/>
+      <c r="J27" s="58"/>
+      <c r="K27" s="24"/>
+      <c r="L27" s="25"/>
+      <c r="M27" s="26"/>
+      <c r="N27" s="24"/>
+      <c r="O27" s="25"/>
+      <c r="P27" s="26"/>
     </row>
     <row r="28" spans="2:44" x14ac:dyDescent="0.25">
-      <c r="B28" s="29"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="40"/>
-      <c r="H28" s="59" t="s">
+      <c r="B28" s="38"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="48"/>
+      <c r="G28" s="49"/>
+      <c r="H28" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="I28" s="59"/>
-      <c r="J28" s="59"/>
-      <c r="K28" s="56"/>
-      <c r="L28" s="57"/>
-      <c r="M28" s="58"/>
-      <c r="N28" s="56"/>
-      <c r="O28" s="57"/>
-      <c r="P28" s="58"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="27"/>
+      <c r="L28" s="28"/>
+      <c r="M28" s="29"/>
+      <c r="N28" s="27"/>
+      <c r="O28" s="28"/>
+      <c r="P28" s="29"/>
     </row>
     <row r="29" spans="2:44" x14ac:dyDescent="0.25">
-      <c r="B29" s="21"/>
-      <c r="C29" s="21"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="21"/>
-      <c r="I29" s="21"/>
-      <c r="J29" s="21"/>
-      <c r="K29" s="21"/>
-      <c r="L29" s="21"/>
-      <c r="M29" s="21"/>
-      <c r="N29" s="21"/>
-      <c r="O29" s="21"/>
-      <c r="P29" s="21"/>
+      <c r="B29" s="59"/>
+      <c r="C29" s="59"/>
+      <c r="D29" s="59"/>
+      <c r="E29" s="59"/>
+      <c r="F29" s="59"/>
+      <c r="G29" s="59"/>
+      <c r="H29" s="59"/>
+      <c r="I29" s="59"/>
+      <c r="J29" s="59"/>
+      <c r="K29" s="59"/>
+      <c r="L29" s="59"/>
+      <c r="M29" s="59"/>
+      <c r="N29" s="59"/>
+      <c r="O29" s="59"/>
+      <c r="P29" s="59"/>
     </row>
     <row r="30" spans="2:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="41"/>
-      <c r="C30" s="42"/>
-      <c r="D30" s="43"/>
+      <c r="B30" s="50"/>
+      <c r="C30" s="51"/>
+      <c r="D30" s="52"/>
       <c r="E30" s="60" t="s">
         <v>17</v>
       </c>
@@ -4013,34 +4031,34 @@
       </c>
       <c r="I30" s="70"/>
       <c r="J30" s="71"/>
-      <c r="K30" s="41"/>
-      <c r="L30" s="42"/>
-      <c r="M30" s="43"/>
-      <c r="N30" s="41"/>
-      <c r="O30" s="42"/>
-      <c r="P30" s="43"/>
+      <c r="K30" s="50"/>
+      <c r="L30" s="51"/>
+      <c r="M30" s="52"/>
+      <c r="N30" s="50"/>
+      <c r="O30" s="51"/>
+      <c r="P30" s="52"/>
     </row>
     <row r="31" spans="2:44" x14ac:dyDescent="0.25">
-      <c r="B31" s="44"/>
-      <c r="C31" s="45"/>
-      <c r="D31" s="46"/>
+      <c r="B31" s="53"/>
+      <c r="C31" s="54"/>
+      <c r="D31" s="55"/>
       <c r="E31" s="63"/>
       <c r="F31" s="64"/>
       <c r="G31" s="65"/>
       <c r="H31" s="72"/>
       <c r="I31" s="73"/>
       <c r="J31" s="74"/>
-      <c r="K31" s="44"/>
-      <c r="L31" s="45"/>
-      <c r="M31" s="46"/>
-      <c r="N31" s="44"/>
-      <c r="O31" s="45"/>
-      <c r="P31" s="46"/>
+      <c r="K31" s="53"/>
+      <c r="L31" s="54"/>
+      <c r="M31" s="55"/>
+      <c r="N31" s="53"/>
+      <c r="O31" s="54"/>
+      <c r="P31" s="55"/>
     </row>
     <row r="32" spans="2:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="44"/>
-      <c r="C32" s="45"/>
-      <c r="D32" s="46"/>
+      <c r="B32" s="53"/>
+      <c r="C32" s="54"/>
+      <c r="D32" s="55"/>
       <c r="E32" s="63"/>
       <c r="F32" s="64"/>
       <c r="G32" s="65"/>
@@ -4049,46 +4067,46 @@
       </c>
       <c r="I32" s="76"/>
       <c r="J32" s="77"/>
-      <c r="K32" s="44"/>
-      <c r="L32" s="45"/>
-      <c r="M32" s="46"/>
-      <c r="N32" s="44"/>
-      <c r="O32" s="45"/>
-      <c r="P32" s="46"/>
+      <c r="K32" s="53"/>
+      <c r="L32" s="54"/>
+      <c r="M32" s="55"/>
+      <c r="N32" s="53"/>
+      <c r="O32" s="54"/>
+      <c r="P32" s="55"/>
     </row>
     <row r="33" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B33" s="44"/>
-      <c r="C33" s="45"/>
-      <c r="D33" s="46"/>
+      <c r="B33" s="53"/>
+      <c r="C33" s="54"/>
+      <c r="D33" s="55"/>
       <c r="E33" s="63"/>
       <c r="F33" s="64"/>
       <c r="G33" s="65"/>
       <c r="H33" s="78"/>
       <c r="I33" s="79"/>
       <c r="J33" s="80"/>
-      <c r="K33" s="44"/>
-      <c r="L33" s="45"/>
-      <c r="M33" s="46"/>
-      <c r="N33" s="44"/>
-      <c r="O33" s="45"/>
-      <c r="P33" s="46"/>
+      <c r="K33" s="53"/>
+      <c r="L33" s="54"/>
+      <c r="M33" s="55"/>
+      <c r="N33" s="53"/>
+      <c r="O33" s="54"/>
+      <c r="P33" s="55"/>
     </row>
     <row r="34" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B34" s="47"/>
-      <c r="C34" s="48"/>
-      <c r="D34" s="49"/>
+      <c r="B34" s="56"/>
+      <c r="C34" s="57"/>
+      <c r="D34" s="58"/>
       <c r="E34" s="66"/>
       <c r="F34" s="67"/>
       <c r="G34" s="68"/>
       <c r="H34" s="81"/>
       <c r="I34" s="82"/>
       <c r="J34" s="83"/>
-      <c r="K34" s="47"/>
-      <c r="L34" s="48"/>
-      <c r="M34" s="49"/>
-      <c r="N34" s="47"/>
-      <c r="O34" s="48"/>
-      <c r="P34" s="49"/>
+      <c r="K34" s="56"/>
+      <c r="L34" s="57"/>
+      <c r="M34" s="58"/>
+      <c r="N34" s="56"/>
+      <c r="O34" s="57"/>
+      <c r="P34" s="58"/>
     </row>
     <row r="37" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
@@ -4096,20 +4114,20 @@
       </c>
     </row>
     <row r="39" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B39" s="85" t="s">
+      <c r="B39" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="85"/>
-      <c r="D39" s="85" t="s">
+      <c r="C39" s="84"/>
+      <c r="D39" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="E39" s="85"/>
-      <c r="F39" s="85" t="s">
+      <c r="E39" s="84"/>
+      <c r="F39" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="G39" s="85"/>
-      <c r="H39" s="85"/>
-      <c r="I39" s="85"/>
+      <c r="G39" s="84"/>
+      <c r="H39" s="84"/>
+      <c r="I39" s="84"/>
       <c r="J39" s="86" t="s">
         <v>22</v>
       </c>
@@ -4118,65 +4136,53 @@
         <v>23</v>
       </c>
       <c r="M39" s="86"/>
-      <c r="N39" s="85" t="s">
+      <c r="N39" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="O39" s="85"/>
-      <c r="P39" s="85"/>
-      <c r="Q39" s="85"/>
+      <c r="O39" s="84"/>
+      <c r="P39" s="84"/>
+      <c r="Q39" s="84"/>
     </row>
     <row r="40" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B40" s="85">
+      <c r="B40" s="84">
         <v>120</v>
       </c>
-      <c r="C40" s="85"/>
-      <c r="D40" s="85">
+      <c r="C40" s="84"/>
+      <c r="D40" s="84">
         <v>20</v>
       </c>
-      <c r="E40" s="85"/>
-      <c r="F40" s="85">
+      <c r="E40" s="84"/>
+      <c r="F40" s="84">
         <v>8</v>
       </c>
-      <c r="G40" s="85"/>
-      <c r="H40" s="85"/>
-      <c r="I40" s="85"/>
+      <c r="G40" s="84"/>
+      <c r="H40" s="84"/>
+      <c r="I40" s="84"/>
       <c r="J40" s="87">
         <v>3.125E-2</v>
       </c>
-      <c r="K40" s="85"/>
+      <c r="K40" s="84"/>
       <c r="L40" s="87">
         <f>J40*F40</f>
         <v>0.25</v>
       </c>
-      <c r="M40" s="85"/>
-      <c r="N40" s="84">
+      <c r="M40" s="84"/>
+      <c r="N40" s="85">
         <f>L40*D40</f>
         <v>5</v>
       </c>
-      <c r="O40" s="84"/>
-      <c r="P40" s="84"/>
-      <c r="Q40" s="84"/>
+      <c r="O40" s="85"/>
+      <c r="P40" s="85"/>
+      <c r="Q40" s="85"/>
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="N40:Q40"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="F39:I39"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="N39:Q39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:I40"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="B30:D34"/>
-    <mergeCell ref="E30:G34"/>
-    <mergeCell ref="H30:J31"/>
-    <mergeCell ref="K30:M34"/>
-    <mergeCell ref="N30:P34"/>
-    <mergeCell ref="H32:J34"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="J2:P2"/>
+    <mergeCell ref="R2:X2"/>
+    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="R12:X12"/>
     <mergeCell ref="N29:P29"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="E23:G23"/>
@@ -4193,12 +4199,24 @@
     <mergeCell ref="E29:G29"/>
     <mergeCell ref="H29:J29"/>
     <mergeCell ref="K29:M29"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="J2:P2"/>
-    <mergeCell ref="R2:X2"/>
-    <mergeCell ref="B12:H12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="R12:X12"/>
+    <mergeCell ref="B30:D34"/>
+    <mergeCell ref="E30:G34"/>
+    <mergeCell ref="H30:J31"/>
+    <mergeCell ref="K30:M34"/>
+    <mergeCell ref="N30:P34"/>
+    <mergeCell ref="H32:J34"/>
+    <mergeCell ref="N40:Q40"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="F39:I39"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="N39:Q39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:I40"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="L40:M40"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4754,6 +4772,16 @@
       <c r="V9" s="7"/>
       <c r="W9" s="7"/>
       <c r="X9" s="5"/>
+      <c r="Z9" s="88"/>
+      <c r="AA9" s="12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="2:44" x14ac:dyDescent="0.25">
+      <c r="Z11" s="17"/>
+      <c r="AA11" s="12" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="12" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="20" t="s">
@@ -5012,23 +5040,23 @@
         <f>X14+1</f>
         <v>7</v>
       </c>
-      <c r="S15" s="7">
+      <c r="S15" s="88">
         <f>R15+1</f>
         <v>8</v>
       </c>
-      <c r="T15" s="11">
+      <c r="T15" s="17">
         <f t="shared" si="10"/>
         <v>9</v>
       </c>
-      <c r="U15" s="7">
+      <c r="U15" s="88">
         <f t="shared" si="10"/>
         <v>10</v>
       </c>
-      <c r="V15" s="7">
+      <c r="V15" s="88">
         <f t="shared" si="10"/>
         <v>11</v>
       </c>
-      <c r="W15" s="7">
+      <c r="W15" s="88">
         <f t="shared" si="10"/>
         <v>12</v>
       </c>
@@ -5314,31 +5342,31 @@
       <c r="F21"/>
     </row>
     <row r="23" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22" t="s">
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22" t="s">
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="I23" s="22"/>
-      <c r="J23" s="22"/>
-      <c r="K23" s="22" t="s">
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="L23" s="22"/>
-      <c r="M23" s="22"/>
-      <c r="N23" s="22" t="s">
+      <c r="L23" s="30"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="O23" s="22"/>
-      <c r="P23" s="22"/>
+      <c r="O23" s="30"/>
+      <c r="P23" s="30"/>
       <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
       <c r="S23" s="2"/>
@@ -5369,121 +5397,121 @@
       <c r="AR23" s="2"/>
     </row>
     <row r="24" spans="2:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="23" t="s">
+      <c r="B24" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="24"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="32" t="s">
+      <c r="C24" s="33"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="F24" s="33"/>
-      <c r="G24" s="34"/>
-      <c r="H24" s="41"/>
-      <c r="I24" s="42"/>
-      <c r="J24" s="43"/>
-      <c r="K24" s="50" t="s">
+      <c r="F24" s="42"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="50"/>
+      <c r="I24" s="51"/>
+      <c r="J24" s="52"/>
+      <c r="K24" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="L24" s="51"/>
-      <c r="M24" s="52"/>
-      <c r="N24" s="50" t="s">
+      <c r="L24" s="22"/>
+      <c r="M24" s="23"/>
+      <c r="N24" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="O24" s="51"/>
-      <c r="P24" s="52"/>
+      <c r="O24" s="22"/>
+      <c r="P24" s="23"/>
     </row>
     <row r="25" spans="2:44" x14ac:dyDescent="0.25">
-      <c r="B25" s="26"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="36"/>
-      <c r="G25" s="37"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="45"/>
-      <c r="J25" s="46"/>
-      <c r="K25" s="53"/>
-      <c r="L25" s="54"/>
-      <c r="M25" s="55"/>
-      <c r="N25" s="53"/>
-      <c r="O25" s="54"/>
-      <c r="P25" s="55"/>
+      <c r="B25" s="35"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="53"/>
+      <c r="I25" s="54"/>
+      <c r="J25" s="55"/>
+      <c r="K25" s="24"/>
+      <c r="L25" s="25"/>
+      <c r="M25" s="26"/>
+      <c r="N25" s="24"/>
+      <c r="O25" s="25"/>
+      <c r="P25" s="26"/>
     </row>
     <row r="26" spans="2:44" x14ac:dyDescent="0.25">
-      <c r="B26" s="26"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="36"/>
-      <c r="G26" s="37"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="45"/>
-      <c r="J26" s="46"/>
-      <c r="K26" s="53"/>
-      <c r="L26" s="54"/>
-      <c r="M26" s="55"/>
-      <c r="N26" s="53"/>
-      <c r="O26" s="54"/>
-      <c r="P26" s="55"/>
+      <c r="B26" s="35"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="44"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="46"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="54"/>
+      <c r="J26" s="55"/>
+      <c r="K26" s="24"/>
+      <c r="L26" s="25"/>
+      <c r="M26" s="26"/>
+      <c r="N26" s="24"/>
+      <c r="O26" s="25"/>
+      <c r="P26" s="26"/>
     </row>
     <row r="27" spans="2:44" x14ac:dyDescent="0.25">
-      <c r="B27" s="26"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="35"/>
-      <c r="F27" s="36"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="47"/>
-      <c r="I27" s="48"/>
-      <c r="J27" s="49"/>
-      <c r="K27" s="53"/>
-      <c r="L27" s="54"/>
-      <c r="M27" s="55"/>
-      <c r="N27" s="53"/>
-      <c r="O27" s="54"/>
-      <c r="P27" s="55"/>
+      <c r="B27" s="35"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="44"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="56"/>
+      <c r="I27" s="57"/>
+      <c r="J27" s="58"/>
+      <c r="K27" s="24"/>
+      <c r="L27" s="25"/>
+      <c r="M27" s="26"/>
+      <c r="N27" s="24"/>
+      <c r="O27" s="25"/>
+      <c r="P27" s="26"/>
     </row>
     <row r="28" spans="2:44" x14ac:dyDescent="0.25">
-      <c r="B28" s="29"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="40"/>
-      <c r="H28" s="59" t="s">
+      <c r="B28" s="38"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="48"/>
+      <c r="G28" s="49"/>
+      <c r="H28" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="I28" s="59"/>
-      <c r="J28" s="59"/>
-      <c r="K28" s="56"/>
-      <c r="L28" s="57"/>
-      <c r="M28" s="58"/>
-      <c r="N28" s="56"/>
-      <c r="O28" s="57"/>
-      <c r="P28" s="58"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="27"/>
+      <c r="L28" s="28"/>
+      <c r="M28" s="29"/>
+      <c r="N28" s="27"/>
+      <c r="O28" s="28"/>
+      <c r="P28" s="29"/>
     </row>
     <row r="29" spans="2:44" x14ac:dyDescent="0.25">
-      <c r="B29" s="21"/>
-      <c r="C29" s="21"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="21"/>
-      <c r="I29" s="21"/>
-      <c r="J29" s="21"/>
-      <c r="K29" s="21"/>
-      <c r="L29" s="21"/>
-      <c r="M29" s="21"/>
-      <c r="N29" s="21"/>
-      <c r="O29" s="21"/>
-      <c r="P29" s="21"/>
+      <c r="B29" s="59"/>
+      <c r="C29" s="59"/>
+      <c r="D29" s="59"/>
+      <c r="E29" s="59"/>
+      <c r="F29" s="59"/>
+      <c r="G29" s="59"/>
+      <c r="H29" s="59"/>
+      <c r="I29" s="59"/>
+      <c r="J29" s="59"/>
+      <c r="K29" s="59"/>
+      <c r="L29" s="59"/>
+      <c r="M29" s="59"/>
+      <c r="N29" s="59"/>
+      <c r="O29" s="59"/>
+      <c r="P29" s="59"/>
     </row>
     <row r="30" spans="2:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="41"/>
-      <c r="C30" s="42"/>
-      <c r="D30" s="43"/>
+      <c r="B30" s="50"/>
+      <c r="C30" s="51"/>
+      <c r="D30" s="52"/>
       <c r="E30" s="60" t="s">
         <v>17</v>
       </c>
@@ -5494,34 +5522,34 @@
       </c>
       <c r="I30" s="70"/>
       <c r="J30" s="71"/>
-      <c r="K30" s="41"/>
-      <c r="L30" s="42"/>
-      <c r="M30" s="43"/>
-      <c r="N30" s="41"/>
-      <c r="O30" s="42"/>
-      <c r="P30" s="43"/>
+      <c r="K30" s="50"/>
+      <c r="L30" s="51"/>
+      <c r="M30" s="52"/>
+      <c r="N30" s="50"/>
+      <c r="O30" s="51"/>
+      <c r="P30" s="52"/>
     </row>
     <row r="31" spans="2:44" x14ac:dyDescent="0.25">
-      <c r="B31" s="44"/>
-      <c r="C31" s="45"/>
-      <c r="D31" s="46"/>
+      <c r="B31" s="53"/>
+      <c r="C31" s="54"/>
+      <c r="D31" s="55"/>
       <c r="E31" s="63"/>
       <c r="F31" s="64"/>
       <c r="G31" s="65"/>
       <c r="H31" s="72"/>
       <c r="I31" s="73"/>
       <c r="J31" s="74"/>
-      <c r="K31" s="44"/>
-      <c r="L31" s="45"/>
-      <c r="M31" s="46"/>
-      <c r="N31" s="44"/>
-      <c r="O31" s="45"/>
-      <c r="P31" s="46"/>
+      <c r="K31" s="53"/>
+      <c r="L31" s="54"/>
+      <c r="M31" s="55"/>
+      <c r="N31" s="53"/>
+      <c r="O31" s="54"/>
+      <c r="P31" s="55"/>
     </row>
     <row r="32" spans="2:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="44"/>
-      <c r="C32" s="45"/>
-      <c r="D32" s="46"/>
+      <c r="B32" s="53"/>
+      <c r="C32" s="54"/>
+      <c r="D32" s="55"/>
       <c r="E32" s="63"/>
       <c r="F32" s="64"/>
       <c r="G32" s="65"/>
@@ -5530,46 +5558,46 @@
       </c>
       <c r="I32" s="76"/>
       <c r="J32" s="77"/>
-      <c r="K32" s="44"/>
-      <c r="L32" s="45"/>
-      <c r="M32" s="46"/>
-      <c r="N32" s="44"/>
-      <c r="O32" s="45"/>
-      <c r="P32" s="46"/>
+      <c r="K32" s="53"/>
+      <c r="L32" s="54"/>
+      <c r="M32" s="55"/>
+      <c r="N32" s="53"/>
+      <c r="O32" s="54"/>
+      <c r="P32" s="55"/>
     </row>
     <row r="33" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B33" s="44"/>
-      <c r="C33" s="45"/>
-      <c r="D33" s="46"/>
+      <c r="B33" s="53"/>
+      <c r="C33" s="54"/>
+      <c r="D33" s="55"/>
       <c r="E33" s="63"/>
       <c r="F33" s="64"/>
       <c r="G33" s="65"/>
       <c r="H33" s="78"/>
       <c r="I33" s="79"/>
       <c r="J33" s="80"/>
-      <c r="K33" s="44"/>
-      <c r="L33" s="45"/>
-      <c r="M33" s="46"/>
-      <c r="N33" s="44"/>
-      <c r="O33" s="45"/>
-      <c r="P33" s="46"/>
+      <c r="K33" s="53"/>
+      <c r="L33" s="54"/>
+      <c r="M33" s="55"/>
+      <c r="N33" s="53"/>
+      <c r="O33" s="54"/>
+      <c r="P33" s="55"/>
     </row>
     <row r="34" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B34" s="47"/>
-      <c r="C34" s="48"/>
-      <c r="D34" s="49"/>
+      <c r="B34" s="56"/>
+      <c r="C34" s="57"/>
+      <c r="D34" s="58"/>
       <c r="E34" s="66"/>
       <c r="F34" s="67"/>
       <c r="G34" s="68"/>
       <c r="H34" s="81"/>
       <c r="I34" s="82"/>
       <c r="J34" s="83"/>
-      <c r="K34" s="47"/>
-      <c r="L34" s="48"/>
-      <c r="M34" s="49"/>
-      <c r="N34" s="47"/>
-      <c r="O34" s="48"/>
-      <c r="P34" s="49"/>
+      <c r="K34" s="56"/>
+      <c r="L34" s="57"/>
+      <c r="M34" s="58"/>
+      <c r="N34" s="56"/>
+      <c r="O34" s="57"/>
+      <c r="P34" s="58"/>
     </row>
     <row r="37" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
@@ -5577,20 +5605,20 @@
       </c>
     </row>
     <row r="39" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B39" s="85" t="s">
+      <c r="B39" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="85"/>
-      <c r="D39" s="85" t="s">
+      <c r="C39" s="84"/>
+      <c r="D39" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="E39" s="85"/>
-      <c r="F39" s="85" t="s">
+      <c r="E39" s="84"/>
+      <c r="F39" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="G39" s="85"/>
-      <c r="H39" s="85"/>
-      <c r="I39" s="85"/>
+      <c r="G39" s="84"/>
+      <c r="H39" s="84"/>
+      <c r="I39" s="84"/>
       <c r="J39" s="86" t="s">
         <v>22</v>
       </c>
@@ -5599,65 +5627,53 @@
         <v>23</v>
       </c>
       <c r="M39" s="86"/>
-      <c r="N39" s="85" t="s">
+      <c r="N39" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="O39" s="85"/>
-      <c r="P39" s="85"/>
-      <c r="Q39" s="85"/>
+      <c r="O39" s="84"/>
+      <c r="P39" s="84"/>
+      <c r="Q39" s="84"/>
     </row>
     <row r="40" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B40" s="85">
+      <c r="B40" s="84">
         <v>120</v>
       </c>
-      <c r="C40" s="85"/>
-      <c r="D40" s="85">
+      <c r="C40" s="84"/>
+      <c r="D40" s="84">
         <v>20</v>
       </c>
-      <c r="E40" s="85"/>
-      <c r="F40" s="85">
+      <c r="E40" s="84"/>
+      <c r="F40" s="84">
         <v>8</v>
       </c>
-      <c r="G40" s="85"/>
-      <c r="H40" s="85"/>
-      <c r="I40" s="85"/>
+      <c r="G40" s="84"/>
+      <c r="H40" s="84"/>
+      <c r="I40" s="84"/>
       <c r="J40" s="87">
         <v>3.125E-2</v>
       </c>
-      <c r="K40" s="85"/>
+      <c r="K40" s="84"/>
       <c r="L40" s="87">
         <f>J40*F40</f>
         <v>0.25</v>
       </c>
-      <c r="M40" s="85"/>
-      <c r="N40" s="84">
+      <c r="M40" s="84"/>
+      <c r="N40" s="85">
         <f>L40*D40</f>
         <v>5</v>
       </c>
-      <c r="O40" s="84"/>
-      <c r="P40" s="84"/>
-      <c r="Q40" s="84"/>
+      <c r="O40" s="85"/>
+      <c r="P40" s="85"/>
+      <c r="Q40" s="85"/>
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="N40:Q40"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="F39:I39"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="N39:Q39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:I40"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="B30:D34"/>
-    <mergeCell ref="E30:G34"/>
-    <mergeCell ref="H30:J31"/>
-    <mergeCell ref="K30:M34"/>
-    <mergeCell ref="N30:P34"/>
-    <mergeCell ref="H32:J34"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="J2:P2"/>
+    <mergeCell ref="R2:X2"/>
+    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="R12:X12"/>
     <mergeCell ref="N29:P29"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="E23:G23"/>
@@ -5674,12 +5690,24 @@
     <mergeCell ref="E29:G29"/>
     <mergeCell ref="H29:J29"/>
     <mergeCell ref="K29:M29"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="J2:P2"/>
-    <mergeCell ref="R2:X2"/>
-    <mergeCell ref="B12:H12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="R12:X12"/>
+    <mergeCell ref="B30:D34"/>
+    <mergeCell ref="E30:G34"/>
+    <mergeCell ref="H30:J31"/>
+    <mergeCell ref="K30:M34"/>
+    <mergeCell ref="N30:P34"/>
+    <mergeCell ref="H32:J34"/>
+    <mergeCell ref="N40:Q40"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="F39:I39"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="N39:Q39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:I40"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="L40:M40"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
